--- a/docs/esempio/Rendicontazione_esempio.xlsx
+++ b/docs/esempio/Rendicontazione_esempio.xlsx
@@ -253,7 +253,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1885" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="406">
   <si>
     <t>COMUNE DI NAPOLI  ·  Assistenza Specialistica</t>
   </si>
@@ -870,7 +870,7 @@
     <t>Comune di Napoli · Assistenza Specialistica all'integrazione scolastica · Febbraio – Marzo 2026 · COOPERATIVA SOCIALE SIRIO</t>
   </si>
   <si>
-    <t>Generato il 09/10/2026 alle 14:38 con Sirio OCR 1.0.0 · 4 fogli firma</t>
+    <t>Generato il 10/10/2026 alle 17:01 con Sirio OCR 1.0.0 · 4 fogli firma</t>
   </si>
   <si>
     <t>FOGLI FIRMA</t>
@@ -1107,7 +1107,7 @@
     <t>Totali per operatore, alunno e istituto</t>
   </si>
   <si>
-    <t>Febbraio – Marzo 2026 · ore e giornate calcolate con formule (SOMMA.PIÙ.SE, CONTA.PIÙ.SE) sul foglio «Dettaglio giornaliero»</t>
+    <t>Febbraio – Marzo 2026 · ore e giornate calcolate con formule (SOMMA.PIÙ.SE, CONTA.SE) sul foglio «Riepilogo»</t>
   </si>
   <si>
     <t>Ore per operatore</t>
@@ -1146,13 +1146,13 @@
     <t>BIANCHI LUCA, NERI MATTEO</t>
   </si>
   <si>
-    <t>Le ore e le giornate sono sommate dal foglio «Dettaglio giornaliero»: correggendo un valore nel dettaglio questi totali si aggiornano automaticamente. % ore su programmate = ore riconosciute ÷ ore programmate.</t>
+    <t>Le ore e le giornate sono sommate dalla tabella del foglio «Riepilogo», collegata alle schede dei fogli firma: correggendo un valore in una scheda questi totali si aggiornano automaticamente. % ore su programmate = ore riconosciute ÷ ore programmate.</t>
   </si>
   <si>
     <t>Legenda e note</t>
   </si>
   <si>
-    <t>Rendicontazione Assistenza Specialistica · Febbraio – Marzo 2026 · Generato il 09/10/2026 alle 14:38</t>
+    <t>Rendicontazione Assistenza Specialistica · Febbraio – Marzo 2026 · Generato il 10/10/2026 alle 17:01</t>
   </si>
   <si>
     <t>Significato dei colori</t>
@@ -1221,7 +1221,7 @@
     <t>Stato, esiti e anomalie riflettono i controlli eseguiti da Sirio OCR al momento della generazione del file.</t>
   </si>
   <si>
-    <t>Le colonne calcolate e i totali sono formule: correggendo un valore nella scheda di un foglio firma si aggiornano i totali della scheda e del Riepilogo; i «Totali per operatore» si basano sul «Dettaglio giornaliero».</t>
+    <t>Le colonne calcolate e i totali sono formule: correggendo un valore nella scheda di un foglio firma si aggiornano i totali della scheda, il «Riepilogo» e i «Totali per operatore». Il «Dettaglio giornaliero» riporta invece i valori al momento della generazione del file: le correzioni vanno fatte nelle schede.</t>
   </si>
   <si>
     <t>Controlli eseguiti</t>
@@ -1368,6 +1368,15 @@
     <t>Orario effettivo presente ma ore effettive non scritte: le ore sono calcolate dall'orario.</t>
   </si>
   <si>
+    <t>W13</t>
+  </si>
+  <si>
+    <t>Possibile foglio duplicato</t>
+  </si>
+  <si>
+    <t>Un altro foglio firma ha lo stesso operatore, alunno, mese e anno: verificare che non sia lo stesso foglio scansionato due volte (le ore sarebbero conteggiate due volte).</t>
+  </si>
+  <si>
     <t>I01</t>
   </si>
   <si>
@@ -1419,7 +1428,7 @@
     <t>Data e ora di generazione</t>
   </si>
   <si>
-    <t>09/10/2026 14:38</t>
+    <t>10/10/2026 17:01</t>
   </si>
   <si>
     <t>Programma</t>
@@ -4009,7 +4018,7 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Sirio OCR · Rendicontazione Assistenza Specialistica&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280&amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 09/10/2026 alle 14:38&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 10/10/2026 alle 17:01&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
@@ -9800,7 +9809,7 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Sirio OCR · Rendicontazione Assistenza Specialistica&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280&amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 09/10/2026 alle 14:38&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 10/10/2026 alle 17:01&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -12459,7 +12468,7 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Sirio OCR · Rendicontazione Assistenza Specialistica&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280&amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 09/10/2026 alle 14:38&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 10/10/2026 alle 17:01&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -14780,7 +14789,7 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Sirio OCR · Rendicontazione Assistenza Specialistica&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280&amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 09/10/2026 alle 14:38&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 10/10/2026 alle 17:01&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -17311,7 +17320,7 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Sirio OCR · Rendicontazione Assistenza Specialistica&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280&amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 09/10/2026 alle 14:38&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 10/10/2026 alle 17:01&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -19940,7 +19949,7 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Sirio OCR · Rendicontazione Assistenza Specialistica&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280&amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 09/10/2026 alle 14:38&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 10/10/2026 alle 17:01&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
   </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -20886,7 +20895,7 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Sirio OCR · Rendicontazione Assistenza Specialistica&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280&amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 09/10/2026 alle 14:38&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 10/10/2026 alle 17:01&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -21008,23 +21017,23 @@
         <v>11</v>
       </c>
       <c r="B7" s="22">
-        <f>COUNTIF('Riepilogo'!$B$12:$B$15,$A7)</f>
+        <f>COUNTIF('Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$7,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>1.0</v>
       </c>
       <c r="C7" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$B$6:$B$86,$A7,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,2,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$7,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,2,1))</f>
         <v>0.0</v>
       </c>
       <c r="D7" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$B$6:$B$86,$A7,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,3,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$7,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,3,1))</f>
         <v>46.25</v>
       </c>
       <c r="E7" s="151">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$B$6:$B$86,$A7)</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$7,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>46.25</v>
       </c>
       <c r="F7" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$M$6:$M$86,'Dettaglio giornaliero'!$B$6:$B$86,$A7)</f>
+        <f>SUMIFS('Riepilogo'!$G$12:$G$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$7,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>44.0</v>
       </c>
       <c r="G7" s="152">
@@ -21032,15 +21041,15 @@
         <v>1.0511363636363635</v>
       </c>
       <c r="H7" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$B$6:$B$86,$A7,'Dettaglio giornaliero'!$P$6:$P$86,"&gt;0")</f>
+        <f>SUMIFS('Riepilogo'!$M$12:$M$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$7,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>23.0</v>
       </c>
       <c r="I7" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$B$6:$B$86,$A7,'Dettaglio giornaliero'!$R$6:$R$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$N$12:$N$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$7,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>0.0</v>
       </c>
       <c r="J7" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$B$6:$B$86,$A7,'Dettaglio giornaliero'!$S$6:$S$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$O$12:$O$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$7,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>0.0</v>
       </c>
       <c r="K7" s="153" t="s">
@@ -21052,23 +21061,23 @@
         <v>106</v>
       </c>
       <c r="B8" s="22">
-        <f>COUNTIF('Riepilogo'!$B$12:$B$15,$A8)</f>
+        <f>COUNTIF('Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$8,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>1.0</v>
       </c>
       <c r="C8" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$B$6:$B$86,$A8,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,2,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$8,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,2,1))</f>
         <v>45.0</v>
       </c>
       <c r="D8" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$B$6:$B$86,$A8,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,3,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$8,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,3,1))</f>
         <v>0.0</v>
       </c>
       <c r="E8" s="151">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$B$6:$B$86,$A8)</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$8,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>45.0</v>
       </c>
       <c r="F8" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$M$6:$M$86,'Dettaglio giornaliero'!$B$6:$B$86,$A8)</f>
+        <f>SUMIFS('Riepilogo'!$G$12:$G$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$8,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>48.0</v>
       </c>
       <c r="G8" s="152">
@@ -21076,15 +21085,15 @@
         <v>0.9375</v>
       </c>
       <c r="H8" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$B$6:$B$86,$A8,'Dettaglio giornaliero'!$P$6:$P$86,"&gt;0")</f>
+        <f>SUMIFS('Riepilogo'!$M$12:$M$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$8,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>15.0</v>
       </c>
       <c r="I8" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$B$6:$B$86,$A8,'Dettaglio giornaliero'!$R$6:$R$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$N$12:$N$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$8,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>0.0</v>
       </c>
       <c r="J8" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$B$6:$B$86,$A8,'Dettaglio giornaliero'!$S$6:$S$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$O$12:$O$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$8,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>1.0</v>
       </c>
       <c r="K8" s="153" t="s">
@@ -21096,23 +21105,23 @@
         <v>126</v>
       </c>
       <c r="B9" s="22">
-        <f>COUNTIF('Riepilogo'!$B$12:$B$15,$A9)</f>
+        <f>COUNTIF('Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$9,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>2.0</v>
       </c>
       <c r="C9" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$B$6:$B$86,$A9,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,2,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$9,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,2,1))</f>
         <v>52.5</v>
       </c>
       <c r="D9" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$B$6:$B$86,$A9,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,3,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$9,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,3,1))</f>
         <v>64.5</v>
       </c>
       <c r="E9" s="151">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$B$6:$B$86,$A9)</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$9,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>117.0</v>
       </c>
       <c r="F9" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$M$6:$M$86,'Dettaglio giornaliero'!$B$6:$B$86,$A9)</f>
+        <f>SUMIFS('Riepilogo'!$G$12:$G$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$9,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>126.0</v>
       </c>
       <c r="G9" s="152">
@@ -21120,15 +21129,15 @@
         <v>0.9285714285714286</v>
       </c>
       <c r="H9" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$B$6:$B$86,$A9,'Dettaglio giornaliero'!$P$6:$P$86,"&gt;0")</f>
+        <f>SUMIFS('Riepilogo'!$M$12:$M$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$9,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>40.0</v>
       </c>
       <c r="I9" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$B$6:$B$86,$A9,'Dettaglio giornaliero'!$R$6:$R$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$N$12:$N$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$9,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>2.0</v>
       </c>
       <c r="J9" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$B$6:$B$86,$A9,'Dettaglio giornaliero'!$S$6:$S$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$O$12:$O$15,'Riepilogo'!$B$12:$B$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$9,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>0.0</v>
       </c>
       <c r="K9" s="153" t="s">
@@ -21232,23 +21241,23 @@
         <v>127</v>
       </c>
       <c r="B14" s="22">
-        <f>COUNTIF('Riepilogo'!$C$12:$C$15,$A14)</f>
+        <f>COUNTIF('Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$14,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>2.0</v>
       </c>
       <c r="C14" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$C$6:$C$86,$A14,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,2,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$14,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,2,1))</f>
         <v>52.5</v>
       </c>
       <c r="D14" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$C$6:$C$86,$A14,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,3,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$14,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,3,1))</f>
         <v>64.5</v>
       </c>
       <c r="E14" s="151">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$C$6:$C$86,$A14)</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$14,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>117.0</v>
       </c>
       <c r="F14" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$M$6:$M$86,'Dettaglio giornaliero'!$C$6:$C$86,$A14)</f>
+        <f>SUMIFS('Riepilogo'!$G$12:$G$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$14,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>126.0</v>
       </c>
       <c r="G14" s="152">
@@ -21256,15 +21265,15 @@
         <v>0.9285714285714286</v>
       </c>
       <c r="H14" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$C$6:$C$86,$A14,'Dettaglio giornaliero'!$P$6:$P$86,"&gt;0")</f>
+        <f>SUMIFS('Riepilogo'!$M$12:$M$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$14,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>40.0</v>
       </c>
       <c r="I14" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$C$6:$C$86,$A14,'Dettaglio giornaliero'!$R$6:$R$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$N$12:$N$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$14,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>2.0</v>
       </c>
       <c r="J14" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$C$6:$C$86,$A14,'Dettaglio giornaliero'!$S$6:$S$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$O$12:$O$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$14,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>0.0</v>
       </c>
       <c r="K14" s="153" t="s">
@@ -21276,23 +21285,23 @@
         <v>15</v>
       </c>
       <c r="B15" s="22">
-        <f>COUNTIF('Riepilogo'!$C$12:$C$15,$A15)</f>
+        <f>COUNTIF('Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$15,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>1.0</v>
       </c>
       <c r="C15" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$C$6:$C$86,$A15,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,2,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$15,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,2,1))</f>
         <v>0.0</v>
       </c>
       <c r="D15" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$C$6:$C$86,$A15,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,3,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$15,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,3,1))</f>
         <v>46.25</v>
       </c>
       <c r="E15" s="151">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$C$6:$C$86,$A15)</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$15,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>46.25</v>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$M$6:$M$86,'Dettaglio giornaliero'!$C$6:$C$86,$A15)</f>
+        <f>SUMIFS('Riepilogo'!$G$12:$G$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$15,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>44.0</v>
       </c>
       <c r="G15" s="152">
@@ -21300,15 +21309,15 @@
         <v>1.0511363636363635</v>
       </c>
       <c r="H15" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$C$6:$C$86,$A15,'Dettaglio giornaliero'!$P$6:$P$86,"&gt;0")</f>
+        <f>SUMIFS('Riepilogo'!$M$12:$M$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$15,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>23.0</v>
       </c>
       <c r="I15" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$C$6:$C$86,$A15,'Dettaglio giornaliero'!$R$6:$R$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$N$12:$N$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$15,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>0.0</v>
       </c>
       <c r="J15" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$C$6:$C$86,$A15,'Dettaglio giornaliero'!$S$6:$S$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$O$12:$O$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$15,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>0.0</v>
       </c>
       <c r="K15" s="153" t="s">
@@ -21320,23 +21329,23 @@
         <v>108</v>
       </c>
       <c r="B16" s="22">
-        <f>COUNTIF('Riepilogo'!$C$12:$C$15,$A16)</f>
+        <f>COUNTIF('Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$16,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>1.0</v>
       </c>
       <c r="C16" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$C$6:$C$86,$A16,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,2,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$16,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,2,1))</f>
         <v>45.0</v>
       </c>
       <c r="D16" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$C$6:$C$86,$A16,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,3,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$16,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,3,1))</f>
         <v>0.0</v>
       </c>
       <c r="E16" s="151">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$C$6:$C$86,$A16)</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$16,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>45.0</v>
       </c>
       <c r="F16" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$M$6:$M$86,'Dettaglio giornaliero'!$C$6:$C$86,$A16)</f>
+        <f>SUMIFS('Riepilogo'!$G$12:$G$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$16,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>48.0</v>
       </c>
       <c r="G16" s="152">
@@ -21344,15 +21353,15 @@
         <v>0.9375</v>
       </c>
       <c r="H16" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$C$6:$C$86,$A16,'Dettaglio giornaliero'!$P$6:$P$86,"&gt;0")</f>
+        <f>SUMIFS('Riepilogo'!$M$12:$M$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$16,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>15.0</v>
       </c>
       <c r="I16" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$C$6:$C$86,$A16,'Dettaglio giornaliero'!$R$6:$R$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$N$12:$N$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$16,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>0.0</v>
       </c>
       <c r="J16" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$C$6:$C$86,$A16,'Dettaglio giornaliero'!$S$6:$S$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$O$12:$O$15,'Riepilogo'!$C$12:$C$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$16,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>1.0</v>
       </c>
       <c r="K16" s="153" t="s">
@@ -21456,23 +21465,23 @@
         <v>8</v>
       </c>
       <c r="B21" s="22">
-        <f>COUNTIF('Riepilogo'!$D$12:$D$15,$A21)</f>
+        <f>COUNTIF('Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$21,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>3.0</v>
       </c>
       <c r="C21" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$D$6:$D$86,$A21,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,2,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$21,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,2,1))</f>
         <v>52.5</v>
       </c>
       <c r="D21" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$D$6:$D$86,$A21,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,3,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$21,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,3,1))</f>
         <v>110.75</v>
       </c>
       <c r="E21" s="151">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$D$6:$D$86,$A21)</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$21,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>163.25</v>
       </c>
       <c r="F21" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$M$6:$M$86,'Dettaglio giornaliero'!$D$6:$D$86,$A21)</f>
+        <f>SUMIFS('Riepilogo'!$G$12:$G$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$21,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>170.0</v>
       </c>
       <c r="G21" s="152">
@@ -21480,15 +21489,15 @@
         <v>0.9602941176470589</v>
       </c>
       <c r="H21" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$D$6:$D$86,$A21,'Dettaglio giornaliero'!$P$6:$P$86,"&gt;0")</f>
+        <f>SUMIFS('Riepilogo'!$M$12:$M$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$21,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>63.0</v>
       </c>
       <c r="I21" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$D$6:$D$86,$A21,'Dettaglio giornaliero'!$R$6:$R$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$N$12:$N$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$21,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>2.0</v>
       </c>
       <c r="J21" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$D$6:$D$86,$A21,'Dettaglio giornaliero'!$S$6:$S$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$O$12:$O$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$21,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>0.0</v>
       </c>
       <c r="K21" s="153" t="s">
@@ -21500,23 +21509,23 @@
         <v>105</v>
       </c>
       <c r="B22" s="22">
-        <f>COUNTIF('Riepilogo'!$D$12:$D$15,$A22)</f>
+        <f>COUNTIF('Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$22,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>1.0</v>
       </c>
       <c r="C22" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$D$6:$D$86,$A22,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,2,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$22,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,2,1))</f>
         <v>45.0</v>
       </c>
       <c r="D22" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$D$6:$D$86,$A22,'Dettaglio giornaliero'!$E$6:$E$86,DATE(2026,3,1))</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$22,"~","~~"),"*","~*"),"?","~?"),'Riepilogo'!$E$12:$E$15,DATE(2026,3,1))</f>
         <v>0.0</v>
       </c>
       <c r="E22" s="151">
-        <f>SUMIFS('Dettaglio giornaliero'!$P$6:$P$86,'Dettaglio giornaliero'!$D$6:$D$86,$A22)</f>
+        <f>SUMIFS('Riepilogo'!$J$12:$J$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$22,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>45.0</v>
       </c>
       <c r="F22" s="20">
-        <f>SUMIFS('Dettaglio giornaliero'!$M$6:$M$86,'Dettaglio giornaliero'!$D$6:$D$86,$A22)</f>
+        <f>SUMIFS('Riepilogo'!$G$12:$G$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$22,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>48.0</v>
       </c>
       <c r="G22" s="152">
@@ -21524,15 +21533,15 @@
         <v>0.9375</v>
       </c>
       <c r="H22" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$D$6:$D$86,$A22,'Dettaglio giornaliero'!$P$6:$P$86,"&gt;0")</f>
+        <f>SUMIFS('Riepilogo'!$M$12:$M$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$22,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>15.0</v>
       </c>
       <c r="I22" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$D$6:$D$86,$A22,'Dettaglio giornaliero'!$R$6:$R$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$N$12:$N$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$22,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>0.0</v>
       </c>
       <c r="J22" s="22">
-        <f>COUNTIFS('Dettaglio giornaliero'!$D$6:$D$86,$A22,'Dettaglio giornaliero'!$S$6:$S$86,"Sì")</f>
+        <f>SUMIFS('Riepilogo'!$O$12:$O$15,'Riepilogo'!$D$12:$D$15,"="&amp;SUBSTITUTE(SUBSTITUTE(SUBSTITUTE($A$22,"~","~~"),"*","~*"),"?","~?"))</f>
         <v>1.0</v>
       </c>
       <c r="K22" s="153" t="s">
@@ -21610,7 +21619,7 @@
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Sirio OCR · Rendicontazione Assistenza Specialistica&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280&amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 09/10/2026 alle 14:38&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 10/10/2026 alle 17:01&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -21621,7 +21630,7 @@
     <tabColor rgb="FF9CA3AF"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.7109375" customWidth="1"/>
@@ -21942,7 +21951,7 @@
       <c r="H25" s="158"/>
       <c r="I25" s="158"/>
     </row>
-    <row r="26" spans="2:9" ht="31.4" customHeight="1">
+    <row r="26" spans="2:9" ht="44.6" customHeight="1">
       <c r="B26" s="167" t="s">
         <v>314</v>
       </c>
@@ -22310,55 +22319,55 @@
       <c r="H47" s="121"/>
       <c r="I47" s="121"/>
     </row>
-    <row r="48" spans="2:9" ht="20" customHeight="1">
+    <row r="48" spans="2:9" ht="44.6" customHeight="1">
       <c r="B48" s="23" t="s">
         <v>371</v>
       </c>
       <c r="C48" s="110" t="s">
-        <v>33</v>
+        <v>372</v>
       </c>
       <c r="D48" s="110"/>
-      <c r="E48" s="122" t="s">
-        <v>93</v>
+      <c r="E48" s="119" t="s">
+        <v>85</v>
       </c>
       <c r="F48" s="121" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G48" s="121"/>
       <c r="H48" s="121"/>
       <c r="I48" s="121"/>
     </row>
-    <row r="49" spans="2:9" ht="31.4" customHeight="1">
+    <row r="49" spans="2:9" ht="20" customHeight="1">
       <c r="B49" s="23" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C49" s="110" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D49" s="110"/>
       <c r="E49" s="122" t="s">
         <v>93</v>
       </c>
       <c r="F49" s="121" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G49" s="121"/>
       <c r="H49" s="121"/>
       <c r="I49" s="121"/>
     </row>
-    <row r="50" spans="2:9" ht="20" customHeight="1">
+    <row r="50" spans="2:9" ht="31.4" customHeight="1">
       <c r="B50" s="23" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C50" s="110" t="s">
-        <v>263</v>
+        <v>34</v>
       </c>
       <c r="D50" s="110"/>
       <c r="E50" s="122" t="s">
         <v>93</v>
       </c>
       <c r="F50" s="121" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G50" s="121"/>
       <c r="H50" s="121"/>
@@ -22366,86 +22375,90 @@
     </row>
     <row r="51" spans="2:9" ht="20" customHeight="1">
       <c r="B51" s="23" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C51" s="110" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D51" s="110"/>
       <c r="E51" s="122" t="s">
         <v>93</v>
       </c>
       <c r="F51" s="121" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G51" s="121"/>
       <c r="H51" s="121"/>
       <c r="I51" s="121"/>
     </row>
-    <row r="52" spans="2:9" ht="31.4" customHeight="1">
+    <row r="52" spans="2:9" ht="20" customHeight="1">
       <c r="B52" s="23" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C52" s="110" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D52" s="110"/>
       <c r="E52" s="122" t="s">
         <v>93</v>
       </c>
       <c r="F52" s="121" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G52" s="121"/>
       <c r="H52" s="121"/>
       <c r="I52" s="121"/>
     </row>
-    <row r="53" spans="2:9" ht="18" customHeight="1">
-      <c r="B53" s="168" t="s">
-        <v>381</v>
-      </c>
-      <c r="C53" s="168"/>
-      <c r="D53" s="168"/>
-      <c r="E53" s="168"/>
-      <c r="F53" s="168"/>
-      <c r="G53" s="168"/>
-      <c r="H53" s="168"/>
-      <c r="I53" s="168"/>
-    </row>
-    <row r="55" spans="2:9" ht="26" customHeight="1">
-      <c r="B55" s="106" t="s">
+    <row r="53" spans="2:9" ht="31.4" customHeight="1">
+      <c r="B53" s="23" t="s">
         <v>382</v>
       </c>
-      <c r="C55" s="106"/>
-      <c r="D55" s="106"/>
-      <c r="E55" s="106"/>
-      <c r="F55" s="106"/>
-      <c r="G55" s="106"/>
-      <c r="H55" s="106"/>
-      <c r="I55" s="106"/>
-    </row>
-    <row r="56" spans="2:9" ht="20" customHeight="1">
-      <c r="B56" s="75" t="s">
+      <c r="C53" s="110" t="s">
+        <v>271</v>
+      </c>
+      <c r="D53" s="110"/>
+      <c r="E53" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" s="121" t="s">
         <v>383</v>
       </c>
-      <c r="C56" s="75"/>
-      <c r="D56" s="75"/>
-      <c r="E56" s="169" t="s">
+      <c r="G53" s="121"/>
+      <c r="H53" s="121"/>
+      <c r="I53" s="121"/>
+    </row>
+    <row r="54" spans="2:9" ht="18" customHeight="1">
+      <c r="B54" s="168" t="s">
         <v>384</v>
       </c>
-      <c r="F56" s="169"/>
-      <c r="G56" s="169"/>
-      <c r="H56" s="169"/>
-      <c r="I56" s="169"/>
+      <c r="C54" s="168"/>
+      <c r="D54" s="168"/>
+      <c r="E54" s="168"/>
+      <c r="F54" s="168"/>
+      <c r="G54" s="168"/>
+      <c r="H54" s="168"/>
+      <c r="I54" s="168"/>
+    </row>
+    <row r="56" spans="2:9" ht="26" customHeight="1">
+      <c r="B56" s="106" t="s">
+        <v>385</v>
+      </c>
+      <c r="C56" s="106"/>
+      <c r="D56" s="106"/>
+      <c r="E56" s="106"/>
+      <c r="F56" s="106"/>
+      <c r="G56" s="106"/>
+      <c r="H56" s="106"/>
+      <c r="I56" s="106"/>
     </row>
     <row r="57" spans="2:9" ht="20" customHeight="1">
       <c r="B57" s="75" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C57" s="75"/>
       <c r="D57" s="75"/>
       <c r="E57" s="169" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F57" s="169"/>
       <c r="G57" s="169"/>
@@ -22454,12 +22467,12 @@
     </row>
     <row r="58" spans="2:9" ht="20" customHeight="1">
       <c r="B58" s="75" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C58" s="75"/>
       <c r="D58" s="75"/>
       <c r="E58" s="169" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F58" s="169"/>
       <c r="G58" s="169"/>
@@ -22468,12 +22481,12 @@
     </row>
     <row r="59" spans="2:9" ht="20" customHeight="1">
       <c r="B59" s="75" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C59" s="75"/>
       <c r="D59" s="75"/>
       <c r="E59" s="169" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F59" s="169"/>
       <c r="G59" s="169"/>
@@ -22482,12 +22495,12 @@
     </row>
     <row r="60" spans="2:9" ht="20" customHeight="1">
       <c r="B60" s="75" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C60" s="75"/>
       <c r="D60" s="75"/>
       <c r="E60" s="169" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F60" s="169"/>
       <c r="G60" s="169"/>
@@ -22496,12 +22509,12 @@
     </row>
     <row r="61" spans="2:9" ht="20" customHeight="1">
       <c r="B61" s="75" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C61" s="75"/>
       <c r="D61" s="75"/>
-      <c r="E61" s="169">
-        <v>4</v>
+      <c r="E61" s="169" t="s">
+        <v>395</v>
       </c>
       <c r="F61" s="169"/>
       <c r="G61" s="169"/>
@@ -22510,65 +22523,63 @@
     </row>
     <row r="62" spans="2:9" ht="20" customHeight="1">
       <c r="B62" s="75" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C62" s="75"/>
       <c r="D62" s="75"/>
-      <c r="E62" s="169" t="s">
-        <v>395</v>
+      <c r="E62" s="169">
+        <v>4</v>
       </c>
       <c r="F62" s="169"/>
       <c r="G62" s="169"/>
       <c r="H62" s="169"/>
       <c r="I62" s="169"/>
     </row>
-    <row r="64" spans="2:9" ht="26" customHeight="1">
-      <c r="B64" s="106" t="s">
-        <v>396</v>
-      </c>
-      <c r="C64" s="106"/>
-      <c r="D64" s="106"/>
-      <c r="E64" s="106"/>
-      <c r="F64" s="106"/>
-      <c r="G64" s="106"/>
-      <c r="H64" s="106"/>
-      <c r="I64" s="106"/>
-    </row>
-    <row r="65" spans="2:9" ht="22" customHeight="1">
-      <c r="B65" s="11" t="s">
+    <row r="63" spans="2:9" ht="20" customHeight="1">
+      <c r="B63" s="75" t="s">
+        <v>397</v>
+      </c>
+      <c r="C63" s="75"/>
+      <c r="D63" s="75"/>
+      <c r="E63" s="169" t="s">
+        <v>398</v>
+      </c>
+      <c r="F63" s="169"/>
+      <c r="G63" s="169"/>
+      <c r="H63" s="169"/>
+      <c r="I63" s="169"/>
+    </row>
+    <row r="65" spans="2:9" ht="26" customHeight="1">
+      <c r="B65" s="106" t="s">
+        <v>399</v>
+      </c>
+      <c r="C65" s="106"/>
+      <c r="D65" s="106"/>
+      <c r="E65" s="106"/>
+      <c r="F65" s="106"/>
+      <c r="G65" s="106"/>
+      <c r="H65" s="106"/>
+      <c r="I65" s="106"/>
+    </row>
+    <row r="66" spans="2:9" ht="22" customHeight="1">
+      <c r="B66" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>398</v>
-      </c>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-    </row>
-    <row r="66" spans="2:9" ht="20" customHeight="1">
-      <c r="B66" s="110" t="s">
-        <v>399</v>
-      </c>
-      <c r="C66" s="110"/>
-      <c r="D66" s="110"/>
-      <c r="E66" s="24">
-        <v>1</v>
-      </c>
-      <c r="F66" s="121" t="s">
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="G66" s="121"/>
-      <c r="H66" s="121"/>
-      <c r="I66" s="121"/>
+      <c r="F66" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
     </row>
     <row r="67" spans="2:9" ht="20" customHeight="1">
       <c r="B67" s="110" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C67" s="110"/>
       <c r="D67" s="110"/>
@@ -22576,19 +22587,35 @@
         <v>1</v>
       </c>
       <c r="F67" s="121" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G67" s="121"/>
       <c r="H67" s="121"/>
       <c r="I67" s="121"/>
     </row>
-    <row r="69" spans="2:9" ht="18" customHeight="1">
-      <c r="B69" s="170" t="s">
+    <row r="68" spans="2:9" ht="20" customHeight="1">
+      <c r="B68" s="110" t="s">
+        <v>404</v>
+      </c>
+      <c r="C68" s="110"/>
+      <c r="D68" s="110"/>
+      <c r="E68" s="24">
+        <v>1</v>
+      </c>
+      <c r="F68" s="121" t="s">
+        <v>405</v>
+      </c>
+      <c r="G68" s="121"/>
+      <c r="H68" s="121"/>
+      <c r="I68" s="121"/>
+    </row>
+    <row r="70" spans="2:9" ht="18" customHeight="1">
+      <c r="B70" s="170" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="97">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="B5:I5"/>
@@ -22661,10 +22688,10 @@
     <mergeCell ref="F51:I51"/>
     <mergeCell ref="C52:D52"/>
     <mergeCell ref="F52:I52"/>
-    <mergeCell ref="B53:I53"/>
-    <mergeCell ref="B55:I55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="E56:I56"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="B54:I54"/>
+    <mergeCell ref="B56:I56"/>
     <mergeCell ref="B57:D57"/>
     <mergeCell ref="E57:I57"/>
     <mergeCell ref="B58:D58"/>
@@ -22677,23 +22704,25 @@
     <mergeCell ref="E61:I61"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="E62:I62"/>
-    <mergeCell ref="B64:I64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="F65:I65"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="E63:I63"/>
+    <mergeCell ref="B65:I65"/>
     <mergeCell ref="B66:D66"/>
     <mergeCell ref="F66:I66"/>
     <mergeCell ref="B67:D67"/>
     <mergeCell ref="F67:I67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="F68:I68"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B69" location="'Riepilogo'!A1" display="‹ Torna al Riepilogo"/>
+    <hyperlink ref="B70" location="'Riepilogo'!A1" display="‹ Torna al Riepilogo"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.6" bottom="0.6" header="0.25" footer="0.25"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Sirio OCR · Rendicontazione Assistenza Specialistica&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280&amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 09/10/2026 alle 14:38&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;8&amp;K6B7280Generato il 10/10/2026 alle 17:01&amp;R&amp;"Calibri,Regular"&amp;8&amp;K6B7280Pagina &amp;P di &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>